--- a/files/九龙-牛头角及九龙湾-皓日.xlsx
+++ b/files/九龙-牛头角及九龙湾-皓日.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="皓日 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -708,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -854,7 +715,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -946,7 +807,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -992,7 +853,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1388,7 +1249,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1434,7 +1295,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1480,7 +1341,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1526,7 +1387,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1672,7 +1533,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1868,7 +1729,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1914,7 +1775,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1960,7 +1821,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2006,7 +1867,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2352,7 +2213,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2398,7 +2259,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2444,7 +2305,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2490,7 +2351,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2774,7 +2635,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2820,7 +2681,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2866,7 +2727,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2912,7 +2773,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2958,7 +2819,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3196,7 +3057,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3242,7 +3103,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3288,7 +3149,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3334,7 +3195,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3380,7 +3241,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3426,7 +3287,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3522,7 +3383,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3660,7 +3521,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3706,7 +3567,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3752,7 +3613,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3798,7 +3659,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3844,7 +3705,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3890,7 +3751,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3936,7 +3797,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3982,7 +3843,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -4074,7 +3935,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4216,7 +4077,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4262,7 +4123,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4308,7 +4169,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4354,7 +4215,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4400,7 +4261,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4446,7 +4307,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4538,7 +4399,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4680,7 +4541,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4726,7 +4587,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4772,7 +4633,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4864,7 +4725,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4910,7 +4771,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4956,7 +4817,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5002,7 +4863,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5140,7 +5001,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5186,7 +5047,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5232,7 +5093,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5324,7 +5185,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5370,7 +5231,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5416,7 +5277,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5462,7 +5323,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5600,7 +5461,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5646,7 +5507,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5692,7 +5553,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5738,7 +5599,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5784,7 +5645,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5830,7 +5691,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5876,7 +5737,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -6014,7 +5875,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6060,7 +5921,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6106,7 +5967,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6152,7 +6013,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6198,7 +6059,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6244,7 +6105,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6290,7 +6151,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6336,7 +6197,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6382,7 +6243,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6428,7 +6289,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6474,7 +6335,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6520,7 +6381,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6566,7 +6427,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6612,7 +6473,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6658,7 +6519,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6750,7 +6611,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6796,7 +6657,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6842,7 +6703,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6888,7 +6749,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6980,7 +6841,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -7026,7 +6887,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7072,7 +6933,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7118,7 +6979,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7164,7 +7025,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7210,7 +7071,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7256,7 +7117,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7302,7 +7163,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7348,7 +7209,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7394,7 +7255,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7440,7 +7301,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7486,7 +7347,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7532,7 +7393,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7578,7 +7439,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7624,7 +7485,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7670,7 +7531,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7716,7 +7577,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7762,7 +7623,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7854,7 +7715,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7900,7 +7761,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7946,7 +7807,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7992,7 +7853,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -8038,7 +7899,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8130,7 +7991,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8176,7 +8037,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8222,7 +8083,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8268,7 +8129,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8314,7 +8175,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8360,7 +8221,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8406,7 +8267,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8452,7 +8313,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8498,7 +8359,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8544,7 +8405,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8590,7 +8451,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8636,7 +8497,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8682,7 +8543,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8728,7 +8589,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8774,7 +8635,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8820,7 +8681,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8866,7 +8727,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8912,7 +8773,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8958,7 +8819,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -9004,7 +8865,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -9050,7 +8911,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9096,7 +8957,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9142,7 +9003,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9188,7 +9049,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9234,7 +9095,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9280,7 +9141,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9372,7 +9233,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9418,7 +9279,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9464,7 +9325,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9510,7 +9371,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9556,7 +9417,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9602,7 +9463,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9648,7 +9509,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9694,7 +9555,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9740,7 +9601,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9786,7 +9647,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9832,7 +9693,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9878,7 +9739,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9924,7 +9785,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9970,7 +9831,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -10016,7 +9877,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10062,7 +9923,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10108,7 +9969,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10154,7 +10015,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10200,7 +10061,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10246,7 +10107,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10292,7 +10153,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10338,7 +10199,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10384,7 +10245,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10430,7 +10291,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10476,7 +10337,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10522,7 +10383,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10568,7 +10429,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10614,7 +10475,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10660,7 +10521,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10706,7 +10567,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10752,7 +10613,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10798,7 +10659,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10844,7 +10705,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -10890,7 +10751,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10936,7 +10797,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10982,7 +10843,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -11028,7 +10889,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -11074,7 +10935,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11120,7 +10981,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11166,7 +11027,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11212,7 +11073,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11258,7 +11119,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11304,7 +11165,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11350,7 +11211,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11396,7 +11257,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11442,7 +11303,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11488,7 +11349,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11534,7 +11395,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11580,7 +11441,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11626,7 +11487,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11672,7 +11533,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11718,7 +11579,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11764,7 +11625,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11810,7 +11671,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -11856,7 +11717,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11902,7 +11763,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11948,7 +11809,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -11994,7 +11855,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -12040,7 +11901,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -12086,7 +11947,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12132,7 +11993,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12178,7 +12039,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12224,7 +12085,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12270,7 +12131,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12316,7 +12177,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12362,7 +12223,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12408,7 +12269,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12454,7 +12315,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12500,7 +12361,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12546,7 +12407,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12592,7 +12453,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12638,7 +12499,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12684,7 +12545,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12730,7 +12591,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12776,7 +12637,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -12822,7 +12683,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -12868,7 +12729,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12914,7 +12775,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -12960,7 +12821,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -13006,7 +12867,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -13052,7 +12913,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -13144,7 +13005,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13190,7 +13051,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13236,7 +13097,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13282,7 +13143,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13328,7 +13189,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13374,7 +13235,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -13420,7 +13281,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -13466,7 +13327,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13512,7 +13373,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13558,7 +13419,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13604,7 +13465,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13650,7 +13511,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13696,7 +13557,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -13742,7 +13603,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -13788,7 +13649,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-29</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13834,7 +13695,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -13930,7 +13791,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -13976,7 +13837,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -14072,7 +13933,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14118,7 +13979,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14164,7 +14025,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14210,7 +14071,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -14256,7 +14117,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14302,7 +14163,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14324,2731 +14185,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>皓日 - 皓日 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>294 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>249 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>19 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 874呎 (3房)
-$2,470万
-$28,261/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 508呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 898呎 (3房)
-$2,636万
-$29,349/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="18" t="inlineStr"/>
-      <c r="J6" s="18" t="inlineStr"/>
-      <c r="K6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 325呎 (1房)
-$710万
-$21,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$700万
-$21,469/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$924万
-$21,005/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,119万
-$22,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$935万
-$21,147/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 326呎 (1房)
-$792万
-$24,279/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$690万
-$21,175/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$892万
-$20,264/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$931万
-$21,054/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 326呎 (1房)
-$790万
-$24,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$760万
-$23,310/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$906万
-$20,602/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,656万
-$21,508/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1,045万
-$22,965/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,337万
-$26,311/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,288万
-$26,073/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$999万
-$22,597/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 325呎 (1房)
-$688万
-$21,175/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$678万
-$20,798/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$876万
-$19,907/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,583万
-$20,556/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$1,023万
-$22,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,296万
-$25,514/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,249万
-$25,291/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$997万
-$22,552/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 325呎 (1房)
-$686万
-$21,092/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$675万
-$20,715/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$881万
-$20,023/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,573万
-$20,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$1,017万
-$22,405/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,291万
-$25,413/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,244万
-$25,190/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$852万
-$26,628/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$995万
-$22,507/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 325呎 (1房)
-$683万
-$21,006/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$673万
-$20,632/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$869万
-$19,745/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1,181万
-$25,947/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,124万
-$22,132/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,265万
-$25,607/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$815万
-$25,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-$1,235万
-$20,865/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$878万
-$19,864/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 326呎 (1房)
-$761万
-$23,353/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$785万
-$24,089/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$857万
-$19,475/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1,176万
-$25,857/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,120万
-$22,055/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,261万
-$25,520/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$812万
-$25,362/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-$1,231万
-$20,792/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$991万
-$22,416/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 326呎 (1房)
-$760万
-$23,328/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$784万
-$24,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$873万
-$19,834/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,656万
-$21,506/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1,154万
-$25,367/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,100万
-$21,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,060万
-$21,455/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$792万
-$24,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-$1,184万
-$20,008/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$968万
-$21,907/呎
-(21年-12月)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 326呎 (1房)
-$758万
-$23,258/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$751万
-$23,034/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$850万
-$19,318/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,597万
-$20,736/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1,147万
-$25,218/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,231万
-$24,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,054万
-$21,338/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 321呎 (1房)
-$821万
-$25,589/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-$1,178万
-$19,899/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$966万
-$21,864/呎
-(21年-12月)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 325呎 (1房)
-$672万
-$20,674/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$781万
-$23,945/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$847万
-$19,241/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,554万
-$20,187/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1,141万
-$25,070/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,270万
-$25,006/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,048万
-$21,223/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 321呎 (1房)
-$739万
-$23,031/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-$1,172万
-$19,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$964万
-$21,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 326呎 (1房)
-$777万
-$23,844/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$659万
-$20,212/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$843万
-$19,164/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,544万
-$20,045/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$970万
-$21,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,082万
-$21,299/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,043万
-$21,105/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$760万
-$23,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-$1,165万
-$19,682/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$962万
-$21,776/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 326呎 (1房)
-$745万
-$22,847/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$742万
-$22,764/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$840万
-$19,089/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,564万
-$20,305/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1,023万
-$22,481/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,076万
-$21,183/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,104万
-$22,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$812万
-$25,366/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-$1,365万
-$23,057/呎
-(21年-12月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$961万
-$21,733/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 325呎 (1房)
-$664万
-$20,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$745万
-$22,853/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$837万
-$19,014/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,492万
-$19,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1,019万
-$22,391/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-$1,070万
-$21,067/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 494呎 (2房)
-$1,100万
-$22,269/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$808万
-$25,262/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 592呎 (3房)
-$1,305万
-$22,047/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 442呎 (2房)
-$942万
-$21,310/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 325呎 (1房)
-$773万
-$23,775/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$774万
-$23,755/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>K | 440呎 (2房)
-$833万
-$18,936/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,484万
-$19,220/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$1,132万
-$24,770/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 511呎 (2房)
-$1,130万
-$22,110/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$1,034万
-$20,805/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$810万
-$25,161/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,148万
-$19,361/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$979万
-$22,106/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$752万
-$22,982/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$778万
-$23,707/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$940万
-$21,327/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,477万
-$19,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
-$957万
-$20,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 511呎 (2房)
-$1,173万
-$22,963/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$1,028万
-$20,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$776万
-$24,084/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,403万
-$23,654/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$849万
-$19,163/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$750万
-$22,948/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$745万
-$22,723/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$828万
-$18,787/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,465万
-$18,981/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
-$954万
-$20,930/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 511呎 (2房)
-$1,152万
-$22,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$1,025万
-$20,628/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$784万
-$24,335/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,138万
-$19,197/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$956万
-$21,582/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$750万
-$22,930/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$754万
-$22,979/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$977万
-$22,150/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,476万
-$19,124/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
-$946万
-$20,748/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$1,053万
-$20,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$1,017万
-$20,463/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$780万
-$24,227/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,152万
-$19,430/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$955万
-$21,549/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$748万
-$22,878/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$752万
-$22,927/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$975万
-$22,116/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,462万
-$18,935/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
-$940万
-$20,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$1,047万
-$20,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-$1,126万
-$22,612/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$754万
-$23,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,123万
-$18,941/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$953万
-$21,517/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$747万
-$22,844/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$751万
-$22,893/呎
-(21年-12月)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$974万
-$22,084/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,419万
-$18,376/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$967万
-$21,164/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$1,042万
-$20,425/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-$1,078万
-$21,645/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$775万
-$24,081/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,117万
-$18,838/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$952万
-$21,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$716万
-$21,899/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$720万
-$21,945/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$815万
-$18,490/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,405万
-$18,194/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$964万
-$21,101/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$1,036万
-$20,314/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-$1,119万
-$22,478/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$773万
-$24,009/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,111万
-$18,735/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$912万
-$20,594/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$745万
-$22,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$749万
-$22,826/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$812万
-$18,415/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,419万
-$18,377/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$1,000万
-$21,880/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$1,030万
-$20,202/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$966万
-$19,439/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$793万
-$24,640/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,105万
-$18,632/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$969万
-$21,874/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$744万
-$22,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$748万
-$22,790/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K28" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$809万
-$18,342/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,405万
-$18,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$998万
-$21,849/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 511呎 (2房)
-$1,106万
-$21,638/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-$1,113万
-$22,343/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$759万
-$23,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,099万
-$18,530/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$929万
-$20,968/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$742万
-$22,706/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$746万
-$22,756/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$800万
-$18,150/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,363万
-$17,659/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
-$904万
-$19,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$1,019万
-$19,982/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$955万
-$19,211/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$789万
-$24,491/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,230万
-$20,744/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$937万
-$21,153/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$607万
-$18,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$745万
-$22,723/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K30" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$797万
-$18,079/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,354万
-$17,536/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
-$901万
-$19,768/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$1,016万
-$19,922/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$952万
-$19,149/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$786万
-$24,419/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,078万
-$18,174/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$965万
-$21,777/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$741万
-$22,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$745万
-$22,704/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$965万
-$21,884/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,305万
-$16,902/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
-$997万
-$21,855/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$980万
-$19,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$926万
-$18,638/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$784万
-$24,345/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,072万
-$18,076/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$771万
-$17,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$710万
-$21,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$743万
-$22,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K32" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$753万
-$17,070/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,289万
-$16,694/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
-$994万
-$21,792/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$949万
-$18,608/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$921万
-$18,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$645万
-$20,022/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,046万
-$17,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$897万
-$20,248/呎
-(21年-12月)</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$597万
-$18,269/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$742万
-$22,619/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K33" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$735万
-$16,671/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,274万
-$16,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$991万
-$21,678/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$919万
-$18,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$916万
-$18,439/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$641万
-$19,913/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$1,025万
-$17,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>G | 443呎 (2房)
-$930万
-$20,993/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>H | 327呎 (1房)
-$729万
-$22,297/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>J | 328呎 (1房)
-$711万
-$21,683/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K34" s="16" t="inlineStr">
-        <is>
-          <t>K | 441呎 (2房)
-$727万
-$16,481/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 772呎 (3房)
-$1,249万
-$16,176/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$967万
-$21,153/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$882万
-$17,302/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$1,042万
-$20,956/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$718万
-$22,283/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>F | 593呎 (3房)
-$990万
-$16,698/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 405呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>H | 290呎 (1房)
-$622万
-$21,452/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>J | 291呎 (1房)
-$621万
-$21,337/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K35" s="19" t="inlineStr">
-        <is>
-          <t>K | 403呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-牛头角及九龙湾-皓日.xlsx
+++ b/files/九龙-牛头角及九龙湾-皓日.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="皓日" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -14185,4 +14373,2731 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>皓日 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 874呎 (3房)
+$2470万
+$28,261/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 898呎 (3房)
+$2636万
+$29,349/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="22" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr"/>
+      <c r="K5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 325呎 (1房)
+$710万
+$21,862/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$700万
+$21,469/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$924万
+$21,005/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1119万
+$22,654/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$935万
+$21,147/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 326呎 (1房)
+$792万
+$24,279/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$690万
+$21,175/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$892万
+$20,264/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$931万
+$21,054/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 326呎 (1房)
+$790万
+$24,230/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$760万
+$23,310/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$906万
+$20,602/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1656万
+$21,508/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1045万
+$22,965/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1337万
+$26,311/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1288万
+$26,073/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$999万
+$22,597/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 325呎 (1房)
+$688万
+$21,175/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$678万
+$20,798/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$876万
+$19,907/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1583万
+$20,556/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$1023万
+$22,540/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1296万
+$25,514/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1249万
+$25,291/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$997万
+$22,552/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 325呎 (1房)
+$686万
+$21,092/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$675万
+$20,715/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$881万
+$20,023/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1573万
+$20,426/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$1017万
+$22,405/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1291万
+$25,413/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1244万
+$25,190/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$852万
+$26,628/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$995万
+$22,507/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 325呎 (1房)
+$683万
+$21,006/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$673万
+$20,632/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$869万
+$19,745/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1181万
+$25,947/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1124万
+$22,132/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1265万
+$25,607/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$815万
+$25,462/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+$1235万
+$20,865/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$878万
+$19,864/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 326呎 (1房)
+$761万
+$23,353/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$785万
+$24,089/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$857万
+$19,475/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1176万
+$25,857/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1120万
+$22,055/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1261万
+$25,520/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$812万
+$25,362/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+$1231万
+$20,792/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$991万
+$22,416/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 326呎 (1房)
+$760万
+$23,328/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$784万
+$24,040/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$873万
+$19,834/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1656万
+$21,506/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1154万
+$25,367/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1100万
+$21,654/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1060万
+$21,455/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$792万
+$24,741/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+$1184万
+$20,008/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$968万
+$21,907/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 326呎 (1房)
+$758万
+$23,258/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$751万
+$23,034/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$850万
+$19,318/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1597万
+$20,736/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1147万
+$25,218/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1231万
+$24,226/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1054万
+$21,338/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 321呎 (1房)
+$821万
+$25,589/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+$1178万
+$19,899/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$966万
+$21,864/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 325呎 (1房)
+$672万
+$20,674/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$781万
+$23,945/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$847万
+$19,241/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1554万
+$20,187/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1141万
+$25,070/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1270万
+$25,006/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1048万
+$21,223/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 321呎 (1房)
+$739万
+$23,031/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+$1172万
+$19,791/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$964万
+$21,821/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 326呎 (1房)
+$777万
+$23,844/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$659万
+$20,212/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$843万
+$19,164/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1544万
+$20,045/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$970万
+$21,374/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1082万
+$21,299/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1043万
+$21,105/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$760万
+$23,750/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+$1165万
+$19,682/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$962万
+$21,776/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 326呎 (1房)
+$745万
+$22,847/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$742万
+$22,764/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$840万
+$19,089/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1564万
+$20,305/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1023万
+$22,481/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1076万
+$21,183/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1104万
+$22,358/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$812万
+$25,366/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+$1365万
+$23,057/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$961万
+$21,733/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 325呎 (1房)
+$664万
+$20,428/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$745万
+$22,853/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$837万
+$19,014/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1492万
+$19,378/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1019万
+$22,391/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+$1070万
+$21,067/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 494呎 (2房)
+$1100万
+$22,269/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$808万
+$25,262/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 592呎 (3房)
+$1305万
+$22,047/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 442呎 (2房)
+$942万
+$21,310/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 325呎 (1房)
+$773万
+$23,775/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$774万
+$23,755/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 440呎 (2房)
+$833万
+$18,936/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1484万
+$19,220/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$1132万
+$24,770/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$1130万
+$22,110/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$1034万
+$20,805/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$810万
+$25,161/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1148万
+$19,361/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$979万
+$22,106/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$752万
+$22,982/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$778万
+$23,707/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$940万
+$21,327/呎
+(22年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1477万
+$19,130/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+$957万
+$20,996/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$1173万
+$22,963/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$1028万
+$20,690/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$776万
+$24,084/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1403万
+$23,654/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$849万
+$19,163/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$750万
+$22,948/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$745万
+$22,723/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$828万
+$18,787/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1465万
+$18,981/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+$954万
+$20,930/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$1152万
+$22,544/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$1025万
+$20,628/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$784万
+$24,335/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1138万
+$19,197/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$956万
+$21,582/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$750万
+$22,930/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$754万
+$22,979/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$977万
+$22,150/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1476万
+$19,124/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+$946万
+$20,748/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$1053万
+$20,649/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$1017万
+$20,463/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$780万
+$24,227/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1152万
+$19,430/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$955万
+$21,549/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$748万
+$22,878/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$752万
+$22,927/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$975万
+$22,116/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1462万
+$18,935/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+$940万
+$20,625/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$1047万
+$20,537/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$1126万
+$22,612/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$754万
+$23,429/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1123万
+$18,941/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$953万
+$21,517/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$747万
+$22,844/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$751万
+$22,893/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$974万
+$22,084/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1419万
+$18,376/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$967万
+$21,164/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$1042万
+$20,425/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$1078万
+$21,645/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$775万
+$24,081/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1117万
+$18,838/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$952万
+$21,485/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$716万
+$21,899/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$720万
+$21,945/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$815万
+$18,490/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1405万
+$18,194/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$964万
+$21,101/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$1036万
+$20,314/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$1119万
+$22,478/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$773万
+$24,009/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1111万
+$18,735/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$912万
+$20,594/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$745万
+$22,774/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$749万
+$22,826/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$812万
+$18,415/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1419万
+$18,377/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$1000万
+$21,880/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$1030万
+$20,202/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$966万
+$19,439/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$793万
+$24,640/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1105万
+$18,632/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$969万
+$21,874/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$744万
+$22,740/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$748万
+$22,790/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$809万
+$18,342/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1405万
+$18,196/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$998万
+$21,849/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$1106万
+$21,638/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$1113万
+$22,343/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$759万
+$23,584/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1099万
+$18,530/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$929万
+$20,968/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$742万
+$22,706/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$746万
+$22,756/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$800万
+$18,150/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1363万
+$17,659/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+$904万
+$19,833/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$1019万
+$19,982/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$955万
+$19,211/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$789万
+$24,491/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1230万
+$20,744/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$937万
+$21,153/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$607万
+$18,554/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$745万
+$22,723/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$797万
+$18,079/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1354万
+$17,536/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+$901万
+$19,768/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$1016万
+$19,922/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$952万
+$19,149/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$786万
+$24,419/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1078万
+$18,174/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$965万
+$21,777/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$741万
+$22,654/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$745万
+$22,704/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$965万
+$21,884/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1305万
+$16,902/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+$997万
+$21,855/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$980万
+$19,210/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$926万
+$18,638/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$784万
+$24,345/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1072万
+$18,076/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$771万
+$17,411/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$710万
+$21,700/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$743万
+$22,655/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$753万
+$17,070/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1289万
+$16,694/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+$994万
+$21,792/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$949万
+$18,608/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$921万
+$18,537/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$645万
+$20,022/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1046万
+$17,637/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$897万
+$20,248/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$597万
+$18,269/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$742万
+$22,619/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$735万
+$16,671/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1274万
+$16,500/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$991万
+$21,678/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$919万
+$18,024/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$916万
+$18,439/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$641万
+$19,913/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$1025万
+$17,292/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>G | 443呎 (2房)
+$930万
+$20,993/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>H | 327呎 (1房)
+$729万
+$22,297/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>J | 328呎 (1房)
+$711万
+$21,683/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>K | 441呎 (2房)
+$727万
+$16,481/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 772呎 (3房)
+$1249万
+$16,176/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$967万
+$21,153/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$882万
+$17,302/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$1042万
+$20,956/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$718万
+$22,283/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 593呎 (3房)
+$990万
+$16,698/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 405呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>H | 290呎 (1房)
+$622万
+$21,452/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$621万
+$21,337/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>K | 403呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-牛头角及九龙湾-皓日.xlsx
+++ b/files/九龙-牛头角及九龙湾-皓日.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-牛头角及九龙湾-皓日.xlsx
+++ b/files/九龙-牛头角及九龙湾-皓日.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J296"/>
+  <dimension ref="A1:N296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -722,6 +726,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -768,6 +792,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>26355000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>29349</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -818,6 +858,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -868,6 +928,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -914,6 +994,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>24700000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>28261</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -949,7 +1045,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -960,6 +1056,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>9242000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>21005</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1006,6 +1118,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>6999000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>21469</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1052,6 +1180,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7105000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>21862</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1102,6 +1246,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1152,6 +1316,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1202,6 +1386,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1252,6 +1456,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1302,6 +1526,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1352,6 +1596,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1402,6 +1666,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1448,6 +1732,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>8916000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>20264</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1494,6 +1794,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6903000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>21175</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1540,6 +1856,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>7915000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>24279</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1586,6 +1918,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>9347000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>21147</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1636,6 +1984,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1686,6 +2054,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1732,6 +2120,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>11191000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>22654</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1782,6 +2186,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1832,6 +2256,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1882,6 +2326,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1928,6 +2392,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>9065000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>20602</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1974,6 +2454,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>7599000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>23310</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2020,6 +2516,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>7899000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>24230</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2066,6 +2578,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>9306000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>21054</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2116,6 +2644,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2166,6 +2714,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2216,6 +2784,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2266,6 +2854,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2316,6 +2924,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2366,6 +2994,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2412,6 +3060,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>8759000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>19907</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2458,6 +3122,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>6780000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>20798</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2504,6 +3184,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>6882000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>21175</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2550,6 +3246,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>9988000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>22597</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2600,6 +3312,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2650,6 +3382,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2696,6 +3448,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>11141200</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>22553</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2742,6 +3510,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>11561590</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>22759</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2788,6 +3572,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>10449000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>22965</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2834,6 +3634,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>16561000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>21508</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2880,6 +3696,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>8810000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>20023</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2926,6 +3758,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>6753000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>20715</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2972,6 +3820,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>6855000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>21092</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3018,6 +3882,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>9968000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>22552</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3068,6 +3948,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3118,6 +4018,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3164,6 +4084,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>10807310</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>21877</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3210,6 +4146,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>11211265</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>22069</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3256,6 +4208,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>10233000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>22540</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3302,6 +4270,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>15828000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>20556</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3348,6 +4332,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>8688000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>19745</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3394,6 +4394,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>6726000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>20632</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3440,6 +4456,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>6827000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>21006</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3486,6 +4518,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>9948000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>22507</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3536,6 +4584,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3582,6 +4650,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>8521000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>26628</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3628,6 +4712,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>10764060</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>21790</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3674,6 +4774,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>11167150</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>21983</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3720,6 +4836,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>10172000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>22405</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3766,6 +4898,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>15728000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>20426</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3812,6 +4960,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>8569000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>19475</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3858,6 +5022,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>7853000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>24089</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3904,6 +5084,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>7613000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>23353</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3950,6 +5146,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>8780000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>19864</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3996,6 +5208,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>12352000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>20865</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4042,6 +5270,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>8148000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>25462</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4088,6 +5332,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>10942250</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>22150</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4134,6 +5394,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>11243000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>22132</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4180,6 +5456,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>10212190</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>22444</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4230,6 +5522,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4276,6 +5588,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>8727000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>19834</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4322,6 +5650,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>7837000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>24040</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4368,6 +5712,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>7605000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>23328</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4414,6 +5774,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>9908000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>22416</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4460,6 +5836,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>12309000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>20792</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4506,6 +5898,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>8116000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>25362</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4552,6 +5960,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>10905055</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>22075</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4598,6 +6022,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>11204000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>22055</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4644,6 +6084,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>10176725</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>22366</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4694,6 +6150,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4740,6 +6216,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>19318</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4786,6 +6278,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>7509000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>23034</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4832,6 +6340,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>7582000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>23258</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4878,6 +6402,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>9683000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>21907</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4924,6 +6464,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>11845000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>20008</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4970,6 +6526,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>7917000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>24741</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5016,6 +6588,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>10599000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>21455</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5062,6 +6650,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>21654</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5108,6 +6712,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>9983830</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>21942</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5154,6 +6774,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>16560000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>21506</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5200,6 +6836,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>8466000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>19241</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5246,6 +6898,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>7806000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>23945</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5292,6 +6960,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>6719000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>20674</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5338,6 +7022,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>9664000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>21864</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5384,6 +7084,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>11780000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>19899</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5430,6 +7146,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>8214000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>25589</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5476,6 +7208,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>10541000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>21338</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5522,6 +7270,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>12307000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>24226</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5568,6 +7332,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>9925010</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>21813</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5614,6 +7394,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>15967000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>20736</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5660,6 +7456,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>8432000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>19164</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5706,6 +7518,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>6589000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>20212</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5752,6 +7580,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>7773000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>23844</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5798,6 +7642,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>9645000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>21821</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5844,6 +7704,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>11716000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>19791</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5890,6 +7766,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>7393000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>23031</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5936,6 +7828,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>10484000</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>21223</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5982,6 +7890,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>10988095</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>21630</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6028,6 +7952,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>9867055</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>21686</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6074,6 +8014,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>15544000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>20187</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6120,6 +8076,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>8399000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>19089</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6166,6 +8138,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>7421000</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>22764</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6212,6 +8200,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>7448000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>22847</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6258,6 +8262,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>9625000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>21776</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6304,6 +8324,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>11652000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>19682</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6350,6 +8386,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>23750</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6396,6 +8448,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>10426000</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>21105</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6442,6 +8510,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>10820000</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>21299</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6488,6 +8572,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>9704000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>21374</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6534,6 +8634,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>15435000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>20045</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6580,6 +8696,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>8366000</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>19014</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6626,6 +8758,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>7450000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>22853</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6672,6 +8820,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>6639000</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>20428</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6718,6 +8882,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>9606000</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>21733</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6764,6 +8944,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>13650000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>23057</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6810,6 +9006,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>8117000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>25366</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6856,6 +9068,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>11045000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>22358</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6902,6 +9130,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>10761000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>21183</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6948,6 +9192,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>10229000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>22481</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6994,6 +9254,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>15635000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>20305</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7040,6 +9316,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>8332000</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>18936</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7086,6 +9378,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>7744000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>23755</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7132,6 +9440,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>7727000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>23775</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7178,6 +9502,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>9419000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>21310</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7224,6 +9564,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>13052000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>22047</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7270,6 +9626,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>8084000</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>25262</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7316,6 +9688,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>11001000</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>22269</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7362,6 +9750,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>10702000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>21067</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7408,6 +9812,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>10188000</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>22391</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7454,6 +9874,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>14921000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>19378</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7500,6 +9936,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>9405000</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>21327</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7546,6 +9998,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>7776000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>23707</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7592,6 +10060,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>7515000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>22982</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7638,6 +10122,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>9793000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>22106</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7684,6 +10184,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>11481000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>19361</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7730,6 +10246,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>8102000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>25161</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7776,6 +10308,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>10340000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>20805</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7822,6 +10370,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>11298000</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>22110</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7868,6 +10432,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>9791800</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>21426</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7914,6 +10494,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>14838000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>19220</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7960,6 +10556,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>8285000</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>18787</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8006,6 +10618,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>7453000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>22723</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8052,6 +10680,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>7504000</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>22948</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8098,6 +10742,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>8489000</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>19163</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8144,6 +10804,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>12133355</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>20461</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>108天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8190,6 +10866,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>7755000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>24084</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8236,6 +10928,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>10283000</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>20690</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8282,6 +10990,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>11734000</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>22963</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8328,6 +11052,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>9574000</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>20996</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8374,6 +11114,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>14768000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>19130</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8420,6 +11176,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>9768000</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>22150</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8466,6 +11238,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>7537000</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>22979</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8512,6 +11300,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>7498000</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>22930</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8558,6 +11362,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>9561000</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>21582</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8604,6 +11424,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>11384000</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>19197</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8650,6 +11486,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>7836000</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>24335</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8696,6 +11548,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>10252000</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>20628</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8742,6 +11610,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>11520000</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>22544</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8788,6 +11672,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>9544000</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>20930</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8834,6 +11734,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>14653000</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>18981</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8880,6 +11796,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>9753000</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>22116</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8926,6 +11858,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>7520000</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>22927</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8972,6 +11920,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>7481000</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>22878</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9018,6 +11982,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>9546000</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>21549</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9064,6 +12044,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>11522000</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>19430</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9110,6 +12106,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>7801000</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>24227</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9156,6 +12168,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>10170000</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>20463</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9202,6 +12230,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>10531000</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>20649</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9248,6 +12292,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>9461000</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>20748</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9294,6 +12354,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>14764000</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>19124</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9340,6 +12416,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>9739000</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>22084</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9386,6 +12478,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>7509000</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>22893</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9432,6 +12540,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>7470000</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>22844</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9478,6 +12602,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>9532000</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>21517</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9524,6 +12664,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>11232000</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>18941</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9570,6 +12726,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>7544000</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>23429</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9616,6 +12788,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>11261000</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>22612</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9662,6 +12850,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>10474000</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>20537</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9708,6 +12912,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>9405000</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>20625</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9754,6 +12974,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>14618000</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>18935</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9800,6 +13036,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>8154000</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>18490</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9846,6 +13098,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>7198000</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>21945</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9892,6 +13160,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>7161000</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>21899</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9938,6 +13222,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>9518000</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>21485</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9984,6 +13284,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>11171000</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>18838</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10030,6 +13346,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>7754000</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>24081</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10076,6 +13408,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>10779000</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>21645</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10122,6 +13470,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>10417000</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>20425</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10168,6 +13532,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>9672000</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>21164</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10214,6 +13594,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>14186000</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>18376</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10260,6 +13656,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>8121000</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>18415</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10306,6 +13718,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>7487000</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>22826</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10352,6 +13780,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>7447000</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>22774</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10398,6 +13842,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>9123000</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>20594</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10444,6 +13904,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>11110000</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>18735</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10490,6 +13966,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>7731000</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>24009</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10536,6 +14028,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>11194000</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>22478</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10582,6 +14090,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>10360000</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>20314</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10628,6 +14152,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>9643000</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>21101</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10674,6 +14214,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>14046000</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>18194</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10720,6 +14276,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>8089000</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>18342</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10766,6 +14338,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>7475000</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>22790</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10812,6 +14400,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>7436000</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>22740</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10858,6 +14462,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>9690000</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>21874</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10904,6 +14524,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>11049000</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>18632</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10950,6 +14586,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>7934000</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>24640</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10996,6 +14648,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>9661000</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>19439</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11042,6 +14710,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>10303000</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>20202</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11088,6 +14772,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>9999000</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>21880</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11134,6 +14834,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>14187000</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>18377</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11180,6 +14896,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>8004000</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>18150</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11226,6 +14958,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>7464000</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>22756</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11272,6 +15020,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>7425000</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>22706</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11318,6 +15082,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>9289000</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>20968</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11364,6 +15144,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>10988000</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>18530</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11410,6 +15206,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>7594000</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>23584</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11456,6 +15268,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>11127000</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>22343</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11502,6 +15330,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>11057000</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>21638</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11548,6 +15392,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>9985000</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>21849</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11594,6 +15454,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>14047000</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>18196</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11640,6 +15516,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>7973000</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>18079</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11686,6 +15578,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>7453000</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>22723</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11732,6 +15640,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>6067000</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>18554</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11778,6 +15702,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>9371000</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>21153</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11824,6 +15764,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>12301000</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>20744</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11870,6 +15826,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>7886000</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>24491</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11916,6 +15888,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>9548000</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>19211</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11962,6 +15950,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>10191000</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>19982</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12008,6 +16012,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>9044000</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>19833</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12054,6 +16074,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>13633000</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>17659</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12100,6 +16136,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>9651000</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>21884</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12146,6 +16198,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>7447000</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>22704</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12192,6 +16260,22 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>7408000</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>22654</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12238,6 +16322,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>9647000</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>21777</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12284,6 +16384,22 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>10777000</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>18174</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12330,6 +16446,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>7863000</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>24419</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12376,6 +16508,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>9517000</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>19149</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12422,6 +16570,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>10160000</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>19922</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12468,6 +16632,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>9014000</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>19768</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12514,6 +16694,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>13538000</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>17536</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12560,6 +16756,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>7528000</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>17070</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12606,6 +16818,22 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>7431000</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>22655</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12652,6 +16880,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>7096000</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>21700</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12698,6 +16942,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>7713000</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>17411</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12744,6 +17004,22 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>10719000</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>18076</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12790,6 +17066,22 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>7839000</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>24345</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12836,6 +17128,22 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>9263000</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>18638</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12882,6 +17190,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>9797000</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>19210</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12928,6 +17252,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>9966000</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>21855</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12974,6 +17314,22 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>13048000</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>16902</v>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13020,6 +17376,22 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>7352000</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>16671</v>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13066,6 +17438,22 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>7419000</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>22619</v>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13112,6 +17500,22 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>5974000</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>18269</v>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13158,6 +17562,22 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>8970000</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>20248</v>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13204,6 +17624,22 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>10459000</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>17637</v>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13250,6 +17686,22 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>6447000</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>20022</v>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13296,6 +17748,22 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>9213000</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>18537</v>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13342,6 +17810,22 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>9490000</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>18608</v>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13388,6 +17872,22 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>9937000</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>21792</v>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13434,6 +17934,22 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>12888000</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>16694</v>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13480,6 +17996,22 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" s="5" t="n">
+        <v>7268000</v>
+      </c>
+      <c r="L277" s="5" t="n">
+        <v>16481</v>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13526,6 +18058,22 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="n">
+        <v>7112000</v>
+      </c>
+      <c r="L278" s="5" t="n">
+        <v>21683</v>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13572,6 +18120,22 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>7291000</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>22297</v>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13618,6 +18182,22 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>9300000</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>20993</v>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13664,6 +18244,22 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>10254000</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>17292</v>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13710,6 +18306,22 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" s="5" t="n">
+        <v>6412000</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>19913</v>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13756,6 +18368,22 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>9164000</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>18439</v>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13802,6 +18430,22 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>9192000</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>18024</v>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13848,6 +18492,22 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>9907000</v>
+      </c>
+      <c r="L285" s="5" t="n">
+        <v>21678</v>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13894,6 +18554,22 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>12738000</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>16500</v>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13944,6 +18620,26 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13990,6 +18686,22 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" s="5" t="n">
+        <v>6209000</v>
+      </c>
+      <c r="L288" s="5" t="n">
+        <v>21337</v>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14036,6 +18748,22 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>6221000</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>21452</v>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14086,6 +18814,26 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14132,6 +18880,22 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>9902000</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>16698</v>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14178,6 +18942,22 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" s="5" t="n">
+        <v>7175000</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>22283</v>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14224,6 +19004,22 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" s="5" t="n">
+        <v>10415000</v>
+      </c>
+      <c r="L293" s="5" t="n">
+        <v>20956</v>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14270,6 +19066,22 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>8824000</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>17302</v>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14316,6 +19128,22 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" s="5" t="n">
+        <v>9667000</v>
+      </c>
+      <c r="L295" s="5" t="n">
+        <v>21153</v>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14362,13 +19190,29 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" s="5" t="n">
+        <v>12488000</v>
+      </c>
+      <c r="L296" s="5" t="n">
+        <v>16176</v>
+      </c>
+      <c r="M296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -14536,7 +19380,7 @@
           <t>A | 874呎 (3房)
 $2470万
 $28,261/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -14560,7 +19404,7 @@
           <t>D | 898呎 (3房)
 $2636万
 $29,349/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -14637,7 +19481,7 @@
           <t>H | 325呎 (1房)
 $710万
 $21,862/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -14645,7 +19489,7 @@
           <t>J | 326呎 (1房)
 $700万
 $21,469/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -14653,7 +19497,7 @@
           <t>K | 440呎 (2房)
 $924万
 $21,005/呎
-(26年-05月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -14692,7 +19536,7 @@
           <t>D | 494呎 (2房)
 $1119万
 $22,654/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -14716,7 +19560,7 @@
           <t>G | 442呎 (2房)
 $935万
 $21,147/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -14724,7 +19568,7 @@
           <t>H | 326呎 (1房)
 $792万
 $24,279/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -14732,7 +19576,7 @@
           <t>J | 326呎 (1房)
 $690万
 $21,175/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -14740,7 +19584,7 @@
           <t>K | 440呎 (2房)
 $892万
 $20,264/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -14803,7 +19647,7 @@
           <t>G | 442呎 (2房)
 $931万
 $21,054/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -14811,7 +19655,7 @@
           <t>H | 326呎 (1房)
 $790万
 $24,230/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -14819,7 +19663,7 @@
           <t>J | 326呎 (1房)
 $760万
 $23,310/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -14827,7 +19671,7 @@
           <t>K | 440呎 (2房)
 $906万
 $20,602/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -14842,7 +19686,7 @@
           <t>A | 770呎 (3房)
 $1656万
 $21,508/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -14850,7 +19694,7 @@
           <t>B | 455呎 (2房)
 $1045万
 $22,965/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -14890,7 +19734,7 @@
           <t>G | 442呎 (2房)
 $999万
 $22,597/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -14898,7 +19742,7 @@
           <t>H | 325呎 (1房)
 $688万
 $21,175/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -14906,7 +19750,7 @@
           <t>J | 326呎 (1房)
 $678万
 $20,798/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -14914,7 +19758,7 @@
           <t>K | 440呎 (2房)
 $876万
 $19,907/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -14929,7 +19773,7 @@
           <t>A | 770呎 (3房)
 $1583万
 $20,556/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -14937,7 +19781,7 @@
           <t>B | 454呎 (2房)
 $1023万
 $22,540/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
@@ -14977,7 +19821,7 @@
           <t>G | 442呎 (2房)
 $997万
 $22,552/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -14985,7 +19829,7 @@
           <t>H | 325呎 (1房)
 $686万
 $21,092/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -14993,7 +19837,7 @@
           <t>J | 326呎 (1房)
 $675万
 $20,715/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -15001,7 +19845,7 @@
           <t>K | 440呎 (2房)
 $881万
 $20,023/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -15016,7 +19860,7 @@
           <t>A | 770呎 (3房)
 $1573万
 $20,426/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -15024,7 +19868,7 @@
           <t>B | 454呎 (2房)
 $1017万
 $22,405/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
@@ -15048,7 +19892,7 @@
           <t>E | 320呎 (1房)
 $852万
 $26,628/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -15064,7 +19908,7 @@
           <t>G | 442呎 (2房)
 $995万
 $22,507/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -15072,7 +19916,7 @@
           <t>H | 325呎 (1房)
 $683万
 $21,006/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -15080,7 +19924,7 @@
           <t>J | 326呎 (1房)
 $673万
 $20,632/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -15088,7 +19932,7 @@
           <t>K | 440呎 (2房)
 $869万
 $19,745/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -15119,7 +19963,7 @@
           <t>C | 508呎 (2房)
 $1124万
 $22,132/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -15135,7 +19979,7 @@
           <t>E | 320呎 (1房)
 $815万
 $25,462/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -15143,7 +19987,7 @@
           <t>F | 592呎 (3房)
 $1235万
 $20,865/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -15151,7 +19995,7 @@
           <t>G | 442呎 (2房)
 $878万
 $19,864/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -15159,7 +20003,7 @@
           <t>H | 326呎 (1房)
 $761万
 $23,353/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -15167,7 +20011,7 @@
           <t>J | 326呎 (1房)
 $785万
 $24,089/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -15175,7 +20019,7 @@
           <t>K | 440呎 (2房)
 $857万
 $19,475/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -15206,7 +20050,7 @@
           <t>C | 508呎 (2房)
 $1120万
 $22,055/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -15222,7 +20066,7 @@
           <t>E | 320呎 (1房)
 $812万
 $25,362/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -15230,7 +20074,7 @@
           <t>F | 592呎 (3房)
 $1231万
 $20,792/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -15238,7 +20082,7 @@
           <t>G | 442呎 (2房)
 $991万
 $22,416/呎
-(22年-01月)</t>
+(22年-01月-25日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -15246,7 +20090,7 @@
           <t>H | 326呎 (1房)
 $760万
 $23,328/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -15254,7 +20098,7 @@
           <t>J | 326呎 (1房)
 $784万
 $24,040/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -15262,7 +20106,7 @@
           <t>K | 440呎 (2房)
 $873万
 $19,834/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -15277,7 +20121,7 @@
           <t>A | 770呎 (3房)
 $1656万
 $21,506/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -15293,7 +20137,7 @@
           <t>C | 508呎 (2房)
 $1100万
 $21,654/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -15301,7 +20145,7 @@
           <t>D | 494呎 (2房)
 $1060万
 $21,455/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -15309,7 +20153,7 @@
           <t>E | 320呎 (1房)
 $792万
 $24,741/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -15317,7 +20161,7 @@
           <t>F | 592呎 (3房)
 $1184万
 $20,008/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -15325,7 +20169,7 @@
           <t>G | 442呎 (2房)
 $968万
 $21,907/呎
-(21年-12月)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -15333,7 +20177,7 @@
           <t>H | 326呎 (1房)
 $758万
 $23,258/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -15341,7 +20185,7 @@
           <t>J | 326呎 (1房)
 $751万
 $23,034/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -15349,7 +20193,7 @@
           <t>K | 440呎 (2房)
 $850万
 $19,318/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -15364,7 +20208,7 @@
           <t>A | 770呎 (3房)
 $1597万
 $20,736/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -15380,7 +20224,7 @@
           <t>C | 508呎 (2房)
 $1231万
 $24,226/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -15388,7 +20232,7 @@
           <t>D | 494呎 (2房)
 $1054万
 $21,338/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -15396,7 +20240,7 @@
           <t>E | 321呎 (1房)
 $821万
 $25,589/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -15404,7 +20248,7 @@
           <t>F | 592呎 (3房)
 $1178万
 $19,899/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -15412,7 +20256,7 @@
           <t>G | 442呎 (2房)
 $966万
 $21,864/呎
-(21年-12月)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -15420,7 +20264,7 @@
           <t>H | 325呎 (1房)
 $672万
 $20,674/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -15428,7 +20272,7 @@
           <t>J | 326呎 (1房)
 $781万
 $23,945/呎
-(22年-01月)</t>
+(22年-01月-09日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -15436,7 +20280,7 @@
           <t>K | 440呎 (2房)
 $847万
 $19,241/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -15451,7 +20295,7 @@
           <t>A | 770呎 (3房)
 $1554万
 $20,187/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -15475,7 +20319,7 @@
           <t>D | 494呎 (2房)
 $1048万
 $21,223/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -15483,7 +20327,7 @@
           <t>E | 321呎 (1房)
 $739万
 $23,031/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -15491,7 +20335,7 @@
           <t>F | 592呎 (3房)
 $1172万
 $19,791/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -15499,7 +20343,7 @@
           <t>G | 442呎 (2房)
 $964万
 $21,821/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -15507,7 +20351,7 @@
           <t>H | 326呎 (1房)
 $777万
 $23,844/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -15515,7 +20359,7 @@
           <t>J | 326呎 (1房)
 $659万
 $20,212/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -15523,7 +20367,7 @@
           <t>K | 440呎 (2房)
 $843万
 $19,164/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -15538,7 +20382,7 @@
           <t>A | 770呎 (3房)
 $1544万
 $20,045/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -15546,7 +20390,7 @@
           <t>B | 454呎 (2房)
 $970万
 $21,374/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -15554,7 +20398,7 @@
           <t>C | 508呎 (2房)
 $1082万
 $21,299/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -15562,7 +20406,7 @@
           <t>D | 494呎 (2房)
 $1043万
 $21,105/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -15570,7 +20414,7 @@
           <t>E | 320呎 (1房)
 $760万
 $23,750/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -15578,7 +20422,7 @@
           <t>F | 592呎 (3房)
 $1165万
 $19,682/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -15586,7 +20430,7 @@
           <t>G | 442呎 (2房)
 $962万
 $21,776/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -15594,7 +20438,7 @@
           <t>H | 326呎 (1房)
 $745万
 $22,847/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -15602,7 +20446,7 @@
           <t>J | 326呎 (1房)
 $742万
 $22,764/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -15610,7 +20454,7 @@
           <t>K | 440呎 (2房)
 $840万
 $19,089/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -15625,7 +20469,7 @@
           <t>A | 770呎 (3房)
 $1564万
 $20,305/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -15633,7 +20477,7 @@
           <t>B | 455呎 (2房)
 $1023万
 $22,481/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -15641,7 +20485,7 @@
           <t>C | 508呎 (2房)
 $1076万
 $21,183/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -15649,7 +20493,7 @@
           <t>D | 494呎 (2房)
 $1104万
 $22,358/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -15657,7 +20501,7 @@
           <t>E | 320呎 (1房)
 $812万
 $25,366/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -15665,7 +20509,7 @@
           <t>F | 592呎 (3房)
 $1365万
 $23,057/呎
-(21年-12月)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -15673,7 +20517,7 @@
           <t>G | 442呎 (2房)
 $961万
 $21,733/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -15681,7 +20525,7 @@
           <t>H | 325呎 (1房)
 $664万
 $20,428/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -15689,7 +20533,7 @@
           <t>J | 326呎 (1房)
 $745万
 $22,853/呎
-(22年-01月)</t>
+(22年-01月-16日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -15697,7 +20541,7 @@
           <t>K | 440呎 (2房)
 $837万
 $19,014/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -15712,7 +20556,7 @@
           <t>A | 770呎 (3房)
 $1492万
 $19,378/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -15720,7 +20564,7 @@
           <t>B | 455呎 (2房)
 $1019万
 $22,391/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -15728,7 +20572,7 @@
           <t>C | 508呎 (2房)
 $1070万
 $21,067/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -15736,7 +20580,7 @@
           <t>D | 494呎 (2房)
 $1100万
 $22,269/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -15744,7 +20588,7 @@
           <t>E | 320呎 (1房)
 $808万
 $25,262/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -15752,7 +20596,7 @@
           <t>F | 592呎 (3房)
 $1305万
 $22,047/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -15760,7 +20604,7 @@
           <t>G | 442呎 (2房)
 $942万
 $21,310/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -15768,7 +20612,7 @@
           <t>H | 325呎 (1房)
 $773万
 $23,775/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -15776,7 +20620,7 @@
           <t>J | 326呎 (1房)
 $774万
 $23,755/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -15784,7 +20628,7 @@
           <t>K | 440呎 (2房)
 $833万
 $18,936/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -15799,7 +20643,7 @@
           <t>A | 772呎 (3房)
 $1484万
 $19,220/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -15815,7 +20659,7 @@
           <t>C | 511呎 (2房)
 $1130万
 $22,110/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -15823,7 +20667,7 @@
           <t>D | 497呎 (2房)
 $1034万
 $20,805/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -15831,7 +20675,7 @@
           <t>E | 322呎 (1房)
 $810万
 $25,161/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -15839,7 +20683,7 @@
           <t>F | 593呎 (3房)
 $1148万
 $19,361/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -15847,7 +20691,7 @@
           <t>G | 443呎 (2房)
 $979万
 $22,106/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -15855,7 +20699,7 @@
           <t>H | 327呎 (1房)
 $752万
 $22,982/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -15863,7 +20707,7 @@
           <t>J | 328呎 (1房)
 $778万
 $23,707/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -15871,7 +20715,7 @@
           <t>K | 441呎 (2房)
 $940万
 $21,327/呎
-(22年-10月)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -15886,7 +20730,7 @@
           <t>A | 772呎 (3房)
 $1477万
 $19,130/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -15894,7 +20738,7 @@
           <t>B | 456呎 (2房)
 $957万
 $20,996/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -15902,7 +20746,7 @@
           <t>C | 511呎 (2房)
 $1173万
 $22,963/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -15910,7 +20754,7 @@
           <t>D | 497呎 (2房)
 $1028万
 $20,690/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -15918,7 +20762,7 @@
           <t>E | 322呎 (1房)
 $776万
 $24,084/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -15934,7 +20778,7 @@
           <t>G | 443呎 (2房)
 $849万
 $19,163/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -15942,7 +20786,7 @@
           <t>H | 327呎 (1房)
 $750万
 $22,948/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -15950,7 +20794,7 @@
           <t>J | 328呎 (1房)
 $745万
 $22,723/呎
-(22年-01月)</t>
+(22年-01月-16日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -15958,7 +20802,7 @@
           <t>K | 441呎 (2房)
 $828万
 $18,787/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -15973,7 +20817,7 @@
           <t>A | 772呎 (3房)
 $1465万
 $18,981/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -15981,7 +20825,7 @@
           <t>B | 456呎 (2房)
 $954万
 $20,930/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -15989,7 +20833,7 @@
           <t>C | 511呎 (2房)
 $1152万
 $22,544/呎
-(22年-01月)</t>
+(22年-01月-16日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -15997,7 +20841,7 @@
           <t>D | 497呎 (2房)
 $1025万
 $20,628/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -16005,7 +20849,7 @@
           <t>E | 322呎 (1房)
 $784万
 $24,335/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -16013,7 +20857,7 @@
           <t>F | 593呎 (3房)
 $1138万
 $19,197/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -16021,7 +20865,7 @@
           <t>G | 443呎 (2房)
 $956万
 $21,582/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -16029,7 +20873,7 @@
           <t>H | 327呎 (1房)
 $750万
 $22,930/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -16037,7 +20881,7 @@
           <t>J | 328呎 (1房)
 $754万
 $22,979/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -16045,7 +20889,7 @@
           <t>K | 441呎 (2房)
 $977万
 $22,150/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -16060,7 +20904,7 @@
           <t>A | 772呎 (3房)
 $1476万
 $19,124/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -16068,7 +20912,7 @@
           <t>B | 456呎 (2房)
 $946万
 $20,748/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -16076,7 +20920,7 @@
           <t>C | 510呎 (2房)
 $1053万
 $20,649/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -16084,7 +20928,7 @@
           <t>D | 497呎 (2房)
 $1017万
 $20,463/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -16092,7 +20936,7 @@
           <t>E | 322呎 (1房)
 $780万
 $24,227/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -16100,7 +20944,7 @@
           <t>F | 593呎 (3房)
 $1152万
 $19,430/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -16108,7 +20952,7 @@
           <t>G | 443呎 (2房)
 $955万
 $21,549/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -16116,7 +20960,7 @@
           <t>H | 327呎 (1房)
 $748万
 $22,878/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -16124,7 +20968,7 @@
           <t>J | 328呎 (1房)
 $752万
 $22,927/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -16132,7 +20976,7 @@
           <t>K | 441呎 (2房)
 $975万
 $22,116/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -16147,7 +20991,7 @@
           <t>A | 772呎 (3房)
 $1462万
 $18,935/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -16155,7 +20999,7 @@
           <t>B | 456呎 (2房)
 $940万
 $20,625/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -16163,7 +21007,7 @@
           <t>C | 510呎 (2房)
 $1047万
 $20,537/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -16171,7 +21015,7 @@
           <t>D | 498呎 (2房)
 $1126万
 $22,612/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -16179,7 +21023,7 @@
           <t>E | 322呎 (1房)
 $754万
 $23,429/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -16187,7 +21031,7 @@
           <t>F | 593呎 (3房)
 $1123万
 $18,941/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -16195,7 +21039,7 @@
           <t>G | 443呎 (2房)
 $953万
 $21,517/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -16203,7 +21047,7 @@
           <t>H | 327呎 (1房)
 $747万
 $22,844/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -16211,7 +21055,7 @@
           <t>J | 328呎 (1房)
 $751万
 $22,893/呎
-(21年-12月)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -16219,7 +21063,7 @@
           <t>K | 441呎 (2房)
 $974万
 $22,084/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -16234,7 +21078,7 @@
           <t>A | 772呎 (3房)
 $1419万
 $18,376/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -16242,7 +21086,7 @@
           <t>B | 457呎 (2房)
 $967万
 $21,164/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -16250,7 +21094,7 @@
           <t>C | 510呎 (2房)
 $1042万
 $20,425/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -16258,7 +21102,7 @@
           <t>D | 498呎 (2房)
 $1078万
 $21,645/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -16266,7 +21110,7 @@
           <t>E | 322呎 (1房)
 $775万
 $24,081/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -16274,7 +21118,7 @@
           <t>F | 593呎 (3房)
 $1117万
 $18,838/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -16282,7 +21126,7 @@
           <t>G | 443呎 (2房)
 $952万
 $21,485/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -16290,7 +21134,7 @@
           <t>H | 327呎 (1房)
 $716万
 $21,899/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -16298,7 +21142,7 @@
           <t>J | 328呎 (1房)
 $720万
 $21,945/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -16306,7 +21150,7 @@
           <t>K | 441呎 (2房)
 $815万
 $18,490/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -16321,7 +21165,7 @@
           <t>A | 772呎 (3房)
 $1405万
 $18,194/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -16329,7 +21173,7 @@
           <t>B | 457呎 (2房)
 $964万
 $21,101/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -16337,7 +21181,7 @@
           <t>C | 510呎 (2房)
 $1036万
 $20,314/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -16345,7 +21189,7 @@
           <t>D | 498呎 (2房)
 $1119万
 $22,478/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -16353,7 +21197,7 @@
           <t>E | 322呎 (1房)
 $773万
 $24,009/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -16361,7 +21205,7 @@
           <t>F | 593呎 (3房)
 $1111万
 $18,735/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -16369,7 +21213,7 @@
           <t>G | 443呎 (2房)
 $912万
 $20,594/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -16377,7 +21221,7 @@
           <t>H | 327呎 (1房)
 $745万
 $22,774/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -16385,7 +21229,7 @@
           <t>J | 328呎 (1房)
 $749万
 $22,826/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -16393,7 +21237,7 @@
           <t>K | 441呎 (2房)
 $812万
 $18,415/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -16408,7 +21252,7 @@
           <t>A | 772呎 (3房)
 $1419万
 $18,377/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -16416,7 +21260,7 @@
           <t>B | 457呎 (2房)
 $1000万
 $21,880/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -16424,7 +21268,7 @@
           <t>C | 510呎 (2房)
 $1030万
 $20,202/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -16432,7 +21276,7 @@
           <t>D | 497呎 (2房)
 $966万
 $19,439/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -16440,7 +21284,7 @@
           <t>E | 322呎 (1房)
 $793万
 $24,640/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -16448,7 +21292,7 @@
           <t>F | 593呎 (3房)
 $1105万
 $18,632/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -16456,7 +21300,7 @@
           <t>G | 443呎 (2房)
 $969万
 $21,874/呎
-(22年-01月)</t>
+(22年-01月-17日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -16464,7 +21308,7 @@
           <t>H | 327呎 (1房)
 $744万
 $22,740/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -16472,7 +21316,7 @@
           <t>J | 328呎 (1房)
 $748万
 $22,790/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -16480,7 +21324,7 @@
           <t>K | 441呎 (2房)
 $809万
 $18,342/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -16495,7 +21339,7 @@
           <t>A | 772呎 (3房)
 $1405万
 $18,196/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -16503,7 +21347,7 @@
           <t>B | 457呎 (2房)
 $998万
 $21,849/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -16511,7 +21355,7 @@
           <t>C | 511呎 (2房)
 $1106万
 $21,638/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -16519,7 +21363,7 @@
           <t>D | 498呎 (2房)
 $1113万
 $22,343/呎
-(22年-01月)</t>
+(22年-01月-09日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -16527,7 +21371,7 @@
           <t>E | 322呎 (1房)
 $759万
 $23,584/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -16535,7 +21379,7 @@
           <t>F | 593呎 (3房)
 $1099万
 $18,530/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -16543,7 +21387,7 @@
           <t>G | 443呎 (2房)
 $929万
 $20,968/呎
-(22年-06月)</t>
+(22年-06月-21日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -16551,7 +21395,7 @@
           <t>H | 327呎 (1房)
 $742万
 $22,706/呎
-(22年-01月)</t>
+(22年-01月-09日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -16559,7 +21403,7 @@
           <t>J | 328呎 (1房)
 $746万
 $22,756/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -16567,7 +21411,7 @@
           <t>K | 441呎 (2房)
 $800万
 $18,150/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -16582,7 +21426,7 @@
           <t>A | 772呎 (3房)
 $1363万
 $17,659/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -16590,7 +21434,7 @@
           <t>B | 456呎 (2房)
 $904万
 $19,833/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -16598,7 +21442,7 @@
           <t>C | 510呎 (2房)
 $1019万
 $19,982/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -16606,7 +21450,7 @@
           <t>D | 497呎 (2房)
 $955万
 $19,211/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -16614,7 +21458,7 @@
           <t>E | 322呎 (1房)
 $789万
 $24,491/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -16622,7 +21466,7 @@
           <t>F | 593呎 (3房)
 $1230万
 $20,744/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -16630,7 +21474,7 @@
           <t>G | 443呎 (2房)
 $937万
 $21,153/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -16638,7 +21482,7 @@
           <t>H | 327呎 (1房)
 $607万
 $18,554/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -16646,7 +21490,7 @@
           <t>J | 328呎 (1房)
 $745万
 $22,723/呎
-(22年-01月)</t>
+(22年-01月-09日)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -16654,7 +21498,7 @@
           <t>K | 441呎 (2房)
 $797万
 $18,079/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -16669,7 +21513,7 @@
           <t>A | 772呎 (3房)
 $1354万
 $17,536/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -16677,7 +21521,7 @@
           <t>B | 456呎 (2房)
 $901万
 $19,768/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -16685,7 +21529,7 @@
           <t>C | 510呎 (2房)
 $1016万
 $19,922/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -16693,7 +21537,7 @@
           <t>D | 497呎 (2房)
 $952万
 $19,149/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -16701,7 +21545,7 @@
           <t>E | 322呎 (1房)
 $786万
 $24,419/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -16709,7 +21553,7 @@
           <t>F | 593呎 (3房)
 $1078万
 $18,174/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -16717,7 +21561,7 @@
           <t>G | 443呎 (2房)
 $965万
 $21,777/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -16725,7 +21569,7 @@
           <t>H | 327呎 (1房)
 $741万
 $22,654/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -16733,7 +21577,7 @@
           <t>J | 328呎 (1房)
 $745万
 $22,704/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -16741,7 +21585,7 @@
           <t>K | 441呎 (2房)
 $965万
 $21,884/呎
-(22年-01月)</t>
+(22年-01月-16日)</t>
         </is>
       </c>
     </row>
@@ -16756,7 +21600,7 @@
           <t>A | 772呎 (3房)
 $1305万
 $16,902/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -16764,7 +21608,7 @@
           <t>B | 456呎 (2房)
 $997万
 $21,855/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -16772,7 +21616,7 @@
           <t>C | 510呎 (2房)
 $980万
 $19,210/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -16780,7 +21624,7 @@
           <t>D | 497呎 (2房)
 $926万
 $18,638/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -16788,7 +21632,7 @@
           <t>E | 322呎 (1房)
 $784万
 $24,345/呎
-(22年-01月)</t>
+(22年-01月-16日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -16796,7 +21640,7 @@
           <t>F | 593呎 (3房)
 $1072万
 $18,076/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -16804,7 +21648,7 @@
           <t>G | 443呎 (2房)
 $771万
 $17,411/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -16812,7 +21656,7 @@
           <t>H | 327呎 (1房)
 $710万
 $21,700/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -16820,7 +21664,7 @@
           <t>J | 328呎 (1房)
 $743万
 $22,655/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -16828,7 +21672,7 @@
           <t>K | 441呎 (2房)
 $753万
 $17,070/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -16843,7 +21687,7 @@
           <t>A | 772呎 (3房)
 $1289万
 $16,694/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -16851,7 +21695,7 @@
           <t>B | 456呎 (2房)
 $994万
 $21,792/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -16859,7 +21703,7 @@
           <t>C | 510呎 (2房)
 $949万
 $18,608/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -16867,7 +21711,7 @@
           <t>D | 497呎 (2房)
 $921万
 $18,537/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -16875,7 +21719,7 @@
           <t>E | 322呎 (1房)
 $645万
 $20,022/呎
-(25年-01月)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -16883,7 +21727,7 @@
           <t>F | 593呎 (3房)
 $1046万
 $17,637/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -16891,7 +21735,7 @@
           <t>G | 443呎 (2房)
 $897万
 $20,248/呎
-(21年-12月)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -16899,7 +21743,7 @@
           <t>H | 327呎 (1房)
 $597万
 $18,269/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -16907,7 +21751,7 @@
           <t>J | 328呎 (1房)
 $742万
 $22,619/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="K32" s="20" t="inlineStr">
@@ -16915,7 +21759,7 @@
           <t>K | 441呎 (2房)
 $735万
 $16,671/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -16930,7 +21774,7 @@
           <t>A | 772呎 (3房)
 $1274万
 $16,500/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -16938,7 +21782,7 @@
           <t>B | 457呎 (2房)
 $991万
 $21,678/呎
-(21年-12月)</t>
+(21年-12月-29日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -16946,7 +21790,7 @@
           <t>C | 510呎 (2房)
 $919万
 $18,024/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -16954,7 +21798,7 @@
           <t>D | 497呎 (2房)
 $916万
 $18,439/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -16962,7 +21806,7 @@
           <t>E | 322呎 (1房)
 $641万
 $19,913/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -16970,7 +21814,7 @@
           <t>F | 593呎 (3房)
 $1025万
 $17,292/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -16978,7 +21822,7 @@
           <t>G | 443呎 (2房)
 $930万
 $20,993/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -16986,7 +21830,7 @@
           <t>H | 327呎 (1房)
 $729万
 $22,297/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -16994,7 +21838,7 @@
           <t>J | 328呎 (1房)
 $711万
 $21,683/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="K33" s="20" t="inlineStr">
@@ -17002,7 +21846,7 @@
           <t>K | 441呎 (2房)
 $727万
 $16,481/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -17017,7 +21861,7 @@
           <t>A | 772呎 (3房)
 $1249万
 $16,176/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -17025,7 +21869,7 @@
           <t>B | 457呎 (2房)
 $967万
 $21,153/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -17033,7 +21877,7 @@
           <t>C | 510呎 (2房)
 $882万
 $17,302/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -17041,7 +21885,7 @@
           <t>D | 497呎 (2房)
 $1042万
 $20,956/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -17049,7 +21893,7 @@
           <t>E | 322呎 (1房)
 $718万
 $22,283/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -17057,7 +21901,7 @@
           <t>F | 593呎 (3房)
 $990万
 $16,698/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -17073,7 +21917,7 @@
           <t>H | 290呎 (1房)
 $622万
 $21,452/呎
-(25年-02月)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -17081,7 +21925,7 @@
           <t>J | 291呎 (1房)
 $621万
 $21,337/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">

--- a/files/九龙-牛头角及九龙湾-皓日.xlsx
+++ b/files/九龙-牛头角及九龙湾-皓日.xlsx
@@ -3459,7 +3459,7 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>108天現金優惠付款計劃</t>
+          <t>300天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
